--- a/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-contra-indications-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-contra-indications-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1|Device|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
